--- a/Assets/StreamingAssets/languages/zh/1.xlsx
+++ b/Assets/StreamingAssets/languages/zh/1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\Resources\story\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\StreamingAssets\languages\zh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560BE0CF-3F85-46EF-BD4D-7820381DB69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57AAC09-291C-4DCC-A15E-56752FE7C412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="830" windowWidth="20000" windowHeight="14450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,13 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Dialogue</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>Avatar</t>
   </si>
@@ -125,6 +119,26 @@
   <si>
     <t>你好来2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>English Name</t>
+  </si>
+  <si>
+    <t>English Dialogue</t>
+  </si>
+  <si>
+    <t>日本語名前</t>
+  </si>
+  <si>
+    <t>日本語会話</t>
   </si>
 </sst>
 </file>
@@ -449,76 +463,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{294B3738-0B50-4E27-88C2-74BD7B9AAF95}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.25" customWidth="1"/>
-    <col min="5" max="5" width="6.1640625" customWidth="1"/>
-    <col min="6" max="6" width="5.58203125" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" customWidth="1"/>
-    <col min="12" max="12" width="9.58203125" customWidth="1"/>
-    <col min="13" max="13" width="9.5" customWidth="1"/>
+    <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5.58203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" hidden="1" customWidth="1"/>
+    <col min="9" max="11" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="9.58203125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" hidden="1" customWidth="1"/>
+    <col min="14" max="16" width="0" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" customWidth="1"/>
+    <col min="18" max="18" width="14.25" customWidth="1"/>
+    <col min="19" max="19" width="10.58203125" customWidth="1"/>
+    <col min="20" max="20" width="13.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -527,39 +561,39 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>-500</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
       </c>
       <c r="H3">
         <v>-400</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K3">
         <v>800</v>
       </c>
       <c r="L3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M3">
         <f>IF(E2&lt;&gt;"",E2,M2)</f>
@@ -578,15 +612,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <f t="shared" ref="M4:M8" si="0">IF(E3&lt;&gt;"",E3,M3)</f>
@@ -605,18 +639,18 @@
         <v>800</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" t="s">
         <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>17</v>
       </c>
       <c r="K5">
         <v>700</v>
@@ -638,15 +672,15 @@
         <v>800</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
@@ -665,18 +699,18 @@
         <v>700</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K7">
         <v>800</v>
@@ -698,18 +732,18 @@
         <v>700</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H8">
         <v>-500</v>
@@ -731,18 +765,18 @@
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9">
         <v>3</v>
